--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20231.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="86">
   <si>
     <t>Mat</t>
   </si>
@@ -85,9 +85,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
@@ -157,9 +154,6 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
     <t>FERRER</t>
   </si>
   <si>
@@ -206,9 +200,6 @@
   </si>
   <si>
     <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
   </si>
   <si>
     <t>VANESA</t>
@@ -681,10 +672,10 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -704,19 +695,19 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>21</v>
       </c>
       <c r="G3">
-        <v>52.5</v>
+        <v>53.85</v>
       </c>
       <c r="H3">
         <v>5.9</v>
@@ -756,10 +747,10 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -768,7 +759,7 @@
         <v>14</v>
       </c>
       <c r="G5">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H5">
         <v>7.1</v>
@@ -873,10 +864,10 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -896,13 +887,13 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -942,10 +933,10 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5">
         <v>18</v>
@@ -1050,10 +1041,10 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1073,19 +1064,19 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>21</v>
       </c>
       <c r="G3">
-        <v>52.5</v>
+        <v>53.85</v>
       </c>
       <c r="H3">
         <v>5.9</v>
@@ -1125,10 +1116,10 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1137,7 +1128,7 @@
         <v>14</v>
       </c>
       <c r="G5">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H5">
         <v>7.1</v>
@@ -1202,7 +1193,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1234,16 +1225,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920213</v>
+        <v>23330051920237</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1257,16 +1248,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920237</v>
+        <v>23330051920242</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1280,16 +1271,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920242</v>
+        <v>23330051920244</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1303,16 +1294,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920244</v>
+        <v>23330051920248</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1326,16 +1317,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920248</v>
+        <v>23330051920254</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1349,16 +1340,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920254</v>
+        <v>23330051920328</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1372,16 +1363,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920328</v>
+        <v>23330051920357</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1395,16 +1386,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920357</v>
+        <v>23330051920257</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1418,16 +1409,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920257</v>
+        <v>23330051920344</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1441,16 +1432,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920344</v>
+        <v>23330051920262</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1464,16 +1455,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920262</v>
+        <v>23330051920330</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1487,16 +1478,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920330</v>
+        <v>23330051920270</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1510,16 +1501,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920270</v>
+        <v>23330051920207</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1533,16 +1524,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920207</v>
+        <v>23330051920276</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1556,16 +1547,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920276</v>
+        <v>23330051920275</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1579,22 +1570,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920275</v>
+        <v>21330051920396</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1602,16 +1593,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920396</v>
+        <v>22330051920286</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1625,39 +1616,39 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920286</v>
+        <v>23330051920227</v>
       </c>
       <c r="B19" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920227</v>
+        <v>23330051920240</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1671,16 +1662,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920240</v>
+        <v>23330051920250</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1694,16 +1685,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920250</v>
+        <v>23330051920333</v>
       </c>
       <c r="B22" t="s">
         <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1717,16 +1708,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920333</v>
+        <v>23330051920272</v>
       </c>
       <c r="B23" t="s">
         <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1740,16 +1731,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920272</v>
+        <v>23330051920327</v>
       </c>
       <c r="B24" t="s">
         <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1763,16 +1754,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920327</v>
+        <v>23330051920277</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="D25" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1786,22 +1777,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920277</v>
+        <v>22330051920277</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1809,47 +1800,24 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920277</v>
+        <v>22330051920305</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>22330051920305</v>
-      </c>
-      <c r="B28" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" t="s">
-        <v>88</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20231.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="55">
   <si>
     <t>Mat</t>
   </si>
@@ -85,49 +85,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>FUENTES</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
     <t>MOSCOSO</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
+    <t>GARZA</t>
+  </si>
+  <si>
+    <t>DEL VALLE</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
   </si>
   <si>
     <t>ARIAS</t>
@@ -136,142 +109,76 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>FERRER</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
     <t>LEYVA</t>
   </si>
   <si>
-    <t>CUAQUEHUA</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
   </si>
   <si>
     <t>SOTO</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>SOSA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>VALERY MIRANDA</t>
-  </si>
-  <si>
-    <t>LUZ YESENIA</t>
-  </si>
-  <si>
-    <t>VIVIANA JOSELIN</t>
-  </si>
-  <si>
-    <t>MIGUEL ENRIQUE</t>
-  </si>
-  <si>
     <t>GISELA GUADALUPE</t>
   </si>
   <si>
     <t>VANESSA</t>
   </si>
   <si>
-    <t>BRISEIDA</t>
-  </si>
-  <si>
     <t>BRISSIA SINAHI</t>
   </si>
   <si>
-    <t>JENNIFER</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>DORIAN</t>
-  </si>
-  <si>
-    <t>VICTORIA VIANNEY</t>
-  </si>
-  <si>
-    <t>ANEL</t>
+    <t>JENNYFER ARIANA</t>
+  </si>
+  <si>
+    <t>ALDRICH ARMANDO</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
   </si>
   <si>
     <t>IGNACIO</t>
   </si>
   <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>IVETTE</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
     <t>ABRAHAM</t>
-  </si>
-  <si>
-    <t>INGRID ISABEL</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>SILVANA</t>
-  </si>
-  <si>
-    <t>SAMANTHA BETHANY</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
   </si>
   <si>
     <t>GAMALIEL</t>
@@ -672,19 +579,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>58.97</v>
+      </c>
+      <c r="H2">
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -864,13 +774,13 @@
         <v>10</v>
       </c>
       <c r="C2">
+        <v>39</v>
+      </c>
+      <c r="D2">
+        <v>39</v>
+      </c>
+      <c r="E2">
         <v>38</v>
-      </c>
-      <c r="D2">
-        <v>38</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1041,19 +951,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>58.97</v>
+      </c>
+      <c r="H2">
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1193,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1225,16 +1138,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920237</v>
+        <v>23330051920328</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1248,16 +1161,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920242</v>
+        <v>23330051920357</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1271,16 +1184,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920244</v>
+        <v>23330051920344</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1294,22 +1207,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920248</v>
+        <v>23330051920356</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1317,22 +1230,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920254</v>
+        <v>23330051920345</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1340,22 +1253,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920328</v>
+        <v>23330051920319</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1363,22 +1276,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920357</v>
+        <v>21330051920396</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1386,16 +1299,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920257</v>
+        <v>23330051920277</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
         <v>50</v>
-      </c>
-      <c r="D9" t="s">
-        <v>68</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1404,420 +1317,98 @@
         <v>10</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920344</v>
+        <v>23330051920336</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
         <v>51</v>
       </c>
-      <c r="D10" t="s">
-        <v>69</v>
-      </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920262</v>
+        <v>22330051920277</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
         <v>52</v>
       </c>
-      <c r="D11" t="s">
-        <v>70</v>
-      </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920330</v>
+        <v>22330051920286</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920270</v>
+        <v>22330051920305</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920207</v>
-      </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920276</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>74</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920275</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920396</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920286</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920227</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920240</v>
-      </c>
-      <c r="B20" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>23330051920250</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" t="s">
-        <v>80</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920333</v>
-      </c>
-      <c r="B22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>23330051920272</v>
-      </c>
-      <c r="B23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>23330051920327</v>
-      </c>
-      <c r="B24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23330051920277</v>
-      </c>
-      <c r="B25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" t="s">
-        <v>83</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920277</v>
-      </c>
-      <c r="B26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" t="s">
-        <v>60</v>
-      </c>
-      <c r="D26" t="s">
-        <v>84</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920305</v>
-      </c>
-      <c r="B27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" t="s">
-        <v>85</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20231.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="61">
   <si>
     <t>Mat</t>
   </si>
@@ -88,55 +88,67 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ALMANZA</t>
+  </si>
+  <si>
+    <t>DORANTES</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MOSCOSO</t>
-  </si>
-  <si>
-    <t>GARZA</t>
-  </si>
-  <si>
-    <t>DEL VALLE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>CIRUELO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>SOTO</t>
   </si>
   <si>
-    <t>GOMEZ</t>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>NATH</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
   </si>
   <si>
     <t>MOLINA</t>
@@ -151,28 +163,34 @@
     <t>GISELA GUADALUPE</t>
   </si>
   <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>BRISSIA SINAHI</t>
-  </si>
-  <si>
-    <t>JENNYFER ARIANA</t>
-  </si>
-  <si>
-    <t>ALDRICH ARMANDO</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>HUGO ANTONIO</t>
   </si>
   <si>
     <t>IGNACIO</t>
   </si>
   <si>
-    <t>ANGEL GABRIEL</t>
+    <t>VANESA BETHSABE</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>AARON ZACHARY</t>
+  </si>
+  <si>
+    <t>KAREN</t>
   </si>
   <si>
     <t>IVETTE</t>
+  </si>
+  <si>
+    <t>ESTEBAN</t>
+  </si>
+  <si>
+    <t>ERIK</t>
   </si>
   <si>
     <t>OSCAR</t>
@@ -660,10 +678,10 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>14</v>
@@ -672,7 +690,7 @@
         <v>73.68000000000001</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -777,16 +795,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>56.41</v>
+      </c>
+      <c r="H2">
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -800,16 +821,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>35.9</v>
+      </c>
+      <c r="H3">
+        <v>5.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -823,16 +847,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>40.54</v>
+      </c>
+      <c r="H4">
+        <v>5.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -846,16 +873,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>47.37</v>
+      </c>
+      <c r="H5">
+        <v>6.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -869,16 +899,19 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>70.83</v>
+      </c>
+      <c r="H6">
+        <v>6.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -892,16 +925,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>93.33</v>
+      </c>
+      <c r="H7">
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -957,16 +993,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>58.97</v>
+        <v>56.41</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -983,16 +1019,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>53.85</v>
+        <v>35.9</v>
       </c>
       <c r="H3">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1009,16 +1045,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>35.14</v>
+        <v>40.54</v>
       </c>
       <c r="H4">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1032,19 +1068,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>73.68000000000001</v>
+        <v>47.37</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1061,16 +1097,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>79.17</v>
+        <v>70.83</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1096,7 +1132,7 @@
         <v>93.33</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1106,7 +1142,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1144,10 +1180,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1161,22 +1197,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920357</v>
+        <v>23330051920220</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1184,22 +1220,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920344</v>
+        <v>23330051920311</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1207,22 +1243,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920356</v>
+        <v>21330051920396</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1230,91 +1266,91 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920345</v>
+        <v>23330051920218</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920319</v>
+        <v>23330051920224</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920396</v>
+        <v>23330051920243</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920277</v>
+        <v>23330051920265</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1325,13 +1361,13 @@
         <v>23330051920336</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1345,22 +1381,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920277</v>
+        <v>23330051920305</v>
       </c>
       <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1368,16 +1404,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920286</v>
+        <v>22330051920276</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1391,24 +1427,70 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920305</v>
+        <v>22330051920277</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920286</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920305</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
         <v>15</v>
       </c>
-      <c r="G13">
+      <c r="G15">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20231.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="98">
   <si>
     <t>Mat</t>
   </si>
@@ -85,13 +85,52 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>FUENTES</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>TEMOXTLE</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>AVILA</t>
+  </si>
+  <si>
+    <t>BERTELY</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
   </si>
   <si>
     <t>ARIAS</t>
@@ -109,9 +148,6 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
@@ -121,19 +157,43 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
   </si>
   <si>
     <t>MACUIXTLE</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
   </si>
   <si>
     <t>SOTO</t>
@@ -160,18 +220,66 @@
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>GISELA GUADALUPE</t>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ANGEL JESUS</t>
+  </si>
+  <si>
+    <t>VIVIANA JOSELIN</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
-    <t>HUGO ANTONIO</t>
+    <t>REGINA DAYTRI</t>
+  </si>
+  <si>
+    <t>MIRIAM</t>
+  </si>
+  <si>
+    <t>ALEX TADEO</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>FERNANDA YAMILET</t>
+  </si>
+  <si>
+    <t>DIANA LAURA</t>
+  </si>
+  <si>
+    <t>KARINA MONSERRATH</t>
+  </si>
+  <si>
+    <t>MARIANA JANET</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>DANIEL DE JESUS</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>GIANCARLO</t>
   </si>
   <si>
     <t>IGNACIO</t>
   </si>
   <si>
+    <t>XIMENA ISABEL</t>
+  </si>
+  <si>
     <t>VANESA BETHSABE</t>
   </si>
   <si>
@@ -197,6 +305,9 @@
   </si>
   <si>
     <t>ABRAHAM</t>
+  </si>
+  <si>
+    <t>EFRAIN DE JESUS</t>
   </si>
   <si>
     <t>GAMALIEL</t>
@@ -1142,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1174,16 +1285,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920328</v>
+        <v>23330051920216</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1197,22 +1308,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920220</v>
+        <v>23330051920248</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1220,22 +1331,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920311</v>
+        <v>23330051920357</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1243,22 +1354,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920396</v>
+        <v>23330051920277</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1266,16 +1377,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920218</v>
+        <v>23330051920220</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1284,21 +1395,21 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920224</v>
+        <v>23330051920228</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1307,21 +1418,21 @@
         <v>11</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920243</v>
+        <v>23330051920233</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1330,21 +1441,21 @@
         <v>11</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920265</v>
+        <v>23330051920234</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1353,35 +1464,35 @@
         <v>11</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920336</v>
+        <v>23330051920236</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920305</v>
+        <v>23330051920271</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
@@ -1390,107 +1501,475 @@
         <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920276</v>
+        <v>23330051920335</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920277</v>
+        <v>23330051920264</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920286</v>
+        <v>23330051920282</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920305</v>
+        <v>23330051920284</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920285</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920342</v>
+      </c>
+      <c r="B17" t="s">
         <v>30</v>
       </c>
-      <c r="D15" t="s">
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920300</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920396</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>23330051920252</v>
+      </c>
+      <c r="B20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" t="s">
+        <v>86</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>23330051920218</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
         <v>60</v>
       </c>
-      <c r="E15" t="s">
+      <c r="D21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>23330051920224</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>23330051920243</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23330051920265</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>23330051920336</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>23330051920305</v>
+      </c>
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>22330051920276</v>
+      </c>
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27" t="s">
         <v>9</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>22330051920277</v>
+      </c>
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>22330051920286</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" t="s">
+        <v>95</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>22330051920291</v>
+      </c>
+      <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
         <v>15</v>
       </c>
-      <c r="G15">
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>22330051920305</v>
+      </c>
+      <c r="B31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20231.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="104">
   <si>
     <t>Mat</t>
   </si>
@@ -124,39 +124,45 @@
     <t>AVILA</t>
   </si>
   <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ALMANZA</t>
+  </si>
+  <si>
+    <t>DORANTES</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>BERTELY</t>
   </si>
   <si>
-    <t>CORTES</t>
-  </si>
-  <si>
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ALMANZA</t>
-  </si>
-  <si>
-    <t>DORANTES</t>
-  </si>
-  <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
@@ -187,33 +193,36 @@
     <t>PABLO</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>NATH</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
     <t>GALINDO</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>MOLINA</t>
   </si>
   <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>NATH</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
     <t>CHIPAHUA</t>
   </si>
   <si>
@@ -262,37 +271,46 @@
     <t>MARIANA JANET</t>
   </si>
   <si>
+    <t>DANIEL DE JESUS</t>
+  </si>
+  <si>
+    <t>JUSTIN GIOVANNI</t>
+  </si>
+  <si>
+    <t>HUGO ANTONIO</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>SERGIO JOSUE</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>XIMENA ISABEL</t>
+  </si>
+  <si>
+    <t>VANESA BETHSABE</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>AARON ZACHARY</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
     <t>MIGUEL</t>
   </si>
   <si>
-    <t>DANIEL DE JESUS</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
+    <t>IVETTE</t>
   </si>
   <si>
     <t>GIANCARLO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>XIMENA ISABEL</t>
-  </si>
-  <si>
-    <t>VANESA BETHSABE</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>AARON ZACHARY</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
   </si>
   <si>
     <t>ESTEBAN</t>
@@ -1253,7 +1271,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1294,7 +1312,7 @@
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1314,10 +1332,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1340,7 +1358,7 @@
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1360,10 +1378,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1383,10 +1401,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1406,10 +1424,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1429,10 +1447,10 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1452,10 +1470,10 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1475,10 +1493,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1501,7 +1519,7 @@
         <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1521,10 +1539,10 @@
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1544,10 +1562,10 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1567,10 +1585,10 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1584,16 +1602,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920284</v>
+        <v>23330051920285</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1607,16 +1625,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920285</v>
+        <v>23330051920308</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1630,22 +1648,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920342</v>
+        <v>23330051920311</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1653,16 +1671,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920300</v>
+        <v>23330051920342</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1676,7 +1694,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920396</v>
+        <v>23330051920332</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
@@ -1685,13 +1703,13 @@
         <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1699,45 +1717,45 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920252</v>
+        <v>21330051920396</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920218</v>
+        <v>23330051920252</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1745,7 +1763,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920224</v>
+        <v>23330051920218</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
@@ -1754,7 +1772,7 @@
         <v>61</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1768,7 +1786,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920243</v>
+        <v>23330051920224</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
@@ -1777,7 +1795,7 @@
         <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1791,7 +1809,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920265</v>
+        <v>23330051920243</v>
       </c>
       <c r="B24" t="s">
         <v>42</v>
@@ -1800,7 +1818,7 @@
         <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1814,22 +1832,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920336</v>
+        <v>23330051920265</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
         <v>64</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1837,22 +1855,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920305</v>
+        <v>23330051920284</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1860,22 +1878,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920276</v>
+        <v>23330051920336</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="D27" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1883,22 +1901,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920277</v>
+        <v>23330051920300</v>
       </c>
       <c r="B28" t="s">
         <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1906,22 +1924,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920286</v>
+        <v>23330051920305</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1929,22 +1947,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920291</v>
+        <v>22330051920276</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1952,24 +1970,93 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920305</v>
+        <v>22330051920277</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="D31" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
       </c>
       <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>22330051920286</v>
+      </c>
+      <c r="B32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>22330051920291</v>
+      </c>
+      <c r="B33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" t="s">
+        <v>102</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
         <v>15</v>
       </c>
-      <c r="G31">
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>22330051920305</v>
+      </c>
+      <c r="B34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20231.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="107">
   <si>
     <t>Mat</t>
   </si>
@@ -106,48 +106,51 @@
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>AVILA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ALMANZA</t>
+  </si>
+  <si>
+    <t>DORANTES</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
+    <t>LAGUNA</t>
   </si>
   <si>
     <t>LOBATO</t>
   </si>
   <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>AVILA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ALMANZA</t>
-  </si>
-  <si>
-    <t>DORANTES</t>
-  </si>
-  <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -181,36 +184,39 @@
     <t>TZITZIHUA</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
+    <t>NATH</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>NATH</t>
-  </si>
-  <si>
     <t>MENDEZ</t>
   </si>
   <si>
@@ -253,52 +259,55 @@
     <t>MIRIAM</t>
   </si>
   <si>
+    <t>FERNANDA YAMILET</t>
+  </si>
+  <si>
+    <t>RAYMUNDO</t>
+  </si>
+  <si>
+    <t>KARINA MONSERRATH</t>
+  </si>
+  <si>
+    <t>MARIANA JANET</t>
+  </si>
+  <si>
+    <t>DANIEL DE JESUS</t>
+  </si>
+  <si>
+    <t>JUSTIN GIOVANNI</t>
+  </si>
+  <si>
+    <t>HUGO ANTONIO</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>SERGIO JOSUE</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>XIMENA ISABEL</t>
+  </si>
+  <si>
+    <t>VANESA BETHSABE</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
     <t>ALEX TADEO</t>
   </si>
   <si>
     <t>EDUARDO</t>
   </si>
   <si>
-    <t>FERNANDA YAMILET</t>
+    <t>AARON ZACHARY</t>
   </si>
   <si>
     <t>DIANA LAURA</t>
-  </si>
-  <si>
-    <t>KARINA MONSERRATH</t>
-  </si>
-  <si>
-    <t>MARIANA JANET</t>
-  </si>
-  <si>
-    <t>DANIEL DE JESUS</t>
-  </si>
-  <si>
-    <t>JUSTIN GIOVANNI</t>
-  </si>
-  <si>
-    <t>HUGO ANTONIO</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>SERGIO JOSUE</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>XIMENA ISABEL</t>
-  </si>
-  <si>
-    <t>VANESA BETHSABE</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>AARON ZACHARY</t>
   </si>
   <si>
     <t>KAREN</t>
@@ -1271,7 +1280,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1312,7 +1321,7 @@
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1332,10 +1341,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1358,7 +1367,7 @@
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1378,10 +1387,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1401,10 +1410,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1424,10 +1433,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1447,10 +1456,10 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1464,16 +1473,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920234</v>
+        <v>23330051920271</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1487,16 +1496,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920236</v>
+        <v>23330051920247</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1510,16 +1519,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920271</v>
+        <v>23330051920264</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1533,22 +1542,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920335</v>
+        <v>23330051920282</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1556,22 +1565,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920264</v>
+        <v>23330051920285</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1579,16 +1588,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920282</v>
+        <v>23330051920308</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1602,16 +1611,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920285</v>
+        <v>23330051920311</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1625,22 +1634,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920308</v>
+        <v>23330051920342</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1648,22 +1657,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920311</v>
+        <v>23330051920332</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1671,22 +1680,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920342</v>
+        <v>21330051920396</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1694,68 +1703,68 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920332</v>
+        <v>23330051920252</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920396</v>
+        <v>23330051920218</v>
       </c>
       <c r="B20" t="s">
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920252</v>
+        <v>23330051920224</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1763,16 +1772,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920218</v>
+        <v>23330051920234</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1786,16 +1795,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920224</v>
+        <v>23330051920236</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1815,10 +1824,10 @@
         <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1832,16 +1841,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920265</v>
+        <v>23330051920335</v>
       </c>
       <c r="B25" t="s">
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1855,22 +1864,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920284</v>
+        <v>23330051920265</v>
       </c>
       <c r="B26" t="s">
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1878,16 +1887,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920336</v>
+        <v>23330051920284</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1901,22 +1910,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920300</v>
+        <v>23330051920336</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1924,16 +1933,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920305</v>
+        <v>23330051920300</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -1947,22 +1956,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920276</v>
+        <v>23330051920305</v>
       </c>
       <c r="B30" t="s">
         <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1970,16 +1979,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920277</v>
+        <v>22330051920276</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -1993,16 +2002,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920286</v>
+        <v>22330051920277</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D32" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -2016,22 +2025,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920291</v>
+        <v>22330051920286</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2039,16 +2048,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>22330051920305</v>
+        <v>22330051920291</v>
       </c>
       <c r="B34" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="D34" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -2057,6 +2066,29 @@
         <v>15</v>
       </c>
       <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>22330051920305</v>
+      </c>
+      <c r="B35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" t="s">
+        <v>106</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20231.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20231.xlsx
@@ -885,7 +885,7 @@
         <v>87.18000000000001</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -911,7 +911,7 @@
         <v>79.48999999999999</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -937,7 +937,7 @@
         <v>83.78</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -963,7 +963,7 @@
         <v>84.20999999999999</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -989,7 +989,7 @@
         <v>91.67</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1015,7 +1015,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20231.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20231.xlsx
@@ -885,7 +885,7 @@
         <v>87.18000000000001</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -911,7 +911,7 @@
         <v>79.48999999999999</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -937,7 +937,7 @@
         <v>83.78</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -963,7 +963,7 @@
         <v>84.20999999999999</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -989,7 +989,7 @@
         <v>91.67</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1015,7 +1015,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
